--- a/duoki_editor/resources/data/blank/服装店-自由画画-2-blank.xlsx
+++ b/duoki_editor/resources/data/blank/服装店-自由画画-2-blank.xlsx
@@ -115,19 +115,19 @@
     <t>duoki</t>
   </si>
   <si>
-    <t>我想要定制一个好看的长袖，你可以帮帮我吗？</t>
+    <t>我想要定制一个好看的外套，你可以帮帮我吗？</t>
   </si>
   <si>
     <t>{user_name}设计师，我们快来看看吧！</t>
   </si>
   <si>
-    <t>请先把绿色边框的长袖放在玩偶上半身吧，准备开始设计啦！</t>
-  </si>
-  <si>
-    <t>快把绿色边框的长袖放在玩偶上半身上吧！</t>
-  </si>
-  <si>
-    <t>时间快来不及了！把绿色边框的长袖放在玩偶上半身上吧！</t>
+    <t>请先把绿色边框的外套放在玩偶上半身吧，准备开始设计啦！</t>
+  </si>
+  <si>
+    <t>快把绿色边框的外套放在玩偶上半身上吧！</t>
+  </si>
+  <si>
+    <t>时间快来不及了！把绿色边框的外套放在玩偶上半身上吧！</t>
   </si>
   <si>
     <t>200402|200435</t>
@@ -136,7 +136,7 @@
     <t>魔镜出来啦！你可以照着图案画，或者画自己想要的图案哦！</t>
   </si>
   <si>
-    <t>画完了把长袖放在魔镜上吧！</t>
+    <t>画完了把外套放在魔镜上吧！</t>
   </si>
   <si>
     <t>时间不多了，再不放在魔镜上，他就要没有魔力了！</t>
@@ -148,7 +148,7 @@
     <t>画完了就点一下屏幕上的按钮哟！</t>
   </si>
   <si>
-    <t>哈哈，我已经帮你把你画的图案变到长袖上了！</t>
+    <t>哈哈，我已经帮你把你画的图案变到外套上了！</t>
   </si>
   <si>
     <t>你可以告诉我你画的是什么吗？比如他是什么东西？他是什么颜色之类的。</t>
@@ -157,13 +157,13 @@
     <t>对了{user_name}，我们使用多奇能力，把他变成你想要的样子吧！让我们一起说，哇塞！多奇！你好神奇！</t>
   </si>
   <si>
-    <t>我帮你把这个长袖用魔法拍照下来存在你的服装店里吧！</t>
+    <t>我帮你把这个外套用魔法拍照下来存在你的服装店里吧！</t>
   </si>
   <si>
     <t>200401</t>
   </si>
   <si>
-    <t>这个长袖忒好看了！我好喜欢！你可真是个好设计师！给你钱！</t>
+    <t>这个外套忒好看了！我好喜欢！你可真是个好设计师！给你钱！</t>
   </si>
   <si>
     <t>Prefect！{user_name}，让我们把他放在地图外面吧！</t>
